--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125098842</v>
+        <v>125098833</v>
       </c>
       <c r="B2" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125098864</v>
+        <v>125098836</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>79795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862123</v>
+        <v>862163</v>
       </c>
       <c r="R3" t="n">
-        <v>7320241</v>
+        <v>7320205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125098836</v>
+        <v>125098832</v>
       </c>
       <c r="B4" t="n">
-        <v>79795</v>
+        <v>92321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -892,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862163</v>
+        <v>862028</v>
       </c>
       <c r="R4" t="n">
-        <v>7320205</v>
+        <v>7320659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125098832</v>
+        <v>125098838</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>79795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -994,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862028</v>
+        <v>862155</v>
       </c>
       <c r="R5" t="n">
-        <v>7320659</v>
+        <v>7320212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125098838</v>
+        <v>125098867</v>
       </c>
       <c r="B6" t="n">
-        <v>79795</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862155</v>
+        <v>862026</v>
       </c>
       <c r="R6" t="n">
-        <v>7320212</v>
+        <v>7320682</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125098833</v>
+        <v>125098864</v>
       </c>
       <c r="B7" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862019</v>
+        <v>862123</v>
       </c>
       <c r="R7" t="n">
-        <v>7320667</v>
+        <v>7320241</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,6 +1269,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125098871</v>
+        <v>125098842</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92285</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,21 +1304,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862032</v>
+        <v>862019</v>
       </c>
       <c r="R8" t="n">
-        <v>7320708</v>
+        <v>7320667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125098867</v>
+        <v>125098871</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>92287</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1402,25 +1402,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862026</v>
+        <v>862032</v>
       </c>
       <c r="R9" t="n">
-        <v>7320682</v>
+        <v>7320708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125098836</v>
+        <v>125098871</v>
       </c>
       <c r="B3" t="n">
-        <v>79795</v>
+        <v>92287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862163</v>
+        <v>862032</v>
       </c>
       <c r="R3" t="n">
-        <v>7320205</v>
+        <v>7320708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125098832</v>
+        <v>125098838</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>79795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862028</v>
+        <v>862155</v>
       </c>
       <c r="R4" t="n">
-        <v>7320659</v>
+        <v>7320212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125098838</v>
+        <v>125098842</v>
       </c>
       <c r="B5" t="n">
-        <v>79795</v>
+        <v>92285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862155</v>
+        <v>862019</v>
       </c>
       <c r="R5" t="n">
-        <v>7320212</v>
+        <v>7320667</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125098867</v>
+        <v>125098864</v>
       </c>
       <c r="B6" t="n">
         <v>92293</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862026</v>
+        <v>862123</v>
       </c>
       <c r="R6" t="n">
-        <v>7320682</v>
+        <v>7320241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1167,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125098864</v>
+        <v>125098836</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>79795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1202,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862123</v>
+        <v>862163</v>
       </c>
       <c r="R7" t="n">
-        <v>7320241</v>
+        <v>7320205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1270,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125098842</v>
+        <v>125098832</v>
       </c>
       <c r="B8" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,21 +1304,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862019</v>
+        <v>862028</v>
       </c>
       <c r="R8" t="n">
-        <v>7320667</v>
+        <v>7320659</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125098871</v>
+        <v>125098867</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1402,25 +1402,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862032</v>
+        <v>862026</v>
       </c>
       <c r="R9" t="n">
-        <v>7320708</v>
+        <v>7320682</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125098833</v>
+        <v>125098871</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862019</v>
+        <v>862032</v>
       </c>
       <c r="R2" t="n">
-        <v>7320667</v>
+        <v>7320708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125098871</v>
+        <v>125098867</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862032</v>
+        <v>862026</v>
       </c>
       <c r="R3" t="n">
-        <v>7320708</v>
+        <v>7320682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125098838</v>
+        <v>125098833</v>
       </c>
       <c r="B4" t="n">
-        <v>79795</v>
+        <v>92321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862155</v>
+        <v>862019</v>
       </c>
       <c r="R4" t="n">
-        <v>7320212</v>
+        <v>7320667</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125098864</v>
+        <v>125098832</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862123</v>
+        <v>862028</v>
       </c>
       <c r="R6" t="n">
-        <v>7320241</v>
+        <v>7320659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1186,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125098836</v>
+        <v>125098838</v>
       </c>
       <c r="B7" t="n">
         <v>79795</v>
@@ -1226,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862163</v>
+        <v>862155</v>
       </c>
       <c r="R7" t="n">
-        <v>7320205</v>
+        <v>7320212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125098832</v>
+        <v>125098836</v>
       </c>
       <c r="B8" t="n">
-        <v>92321</v>
+        <v>79795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862028</v>
+        <v>862163</v>
       </c>
       <c r="R8" t="n">
-        <v>7320659</v>
+        <v>7320205</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125098867</v>
+        <v>125098864</v>
       </c>
       <c r="B9" t="n">
         <v>92293</v>
@@ -1430,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862026</v>
+        <v>862123</v>
       </c>
       <c r="R9" t="n">
-        <v>7320682</v>
+        <v>7320241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,6 +1473,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125098871</v>
+        <v>125098867</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862032</v>
+        <v>862026</v>
       </c>
       <c r="R2" t="n">
-        <v>7320708</v>
+        <v>7320682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125098867</v>
+        <v>125098836</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>79795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862026</v>
+        <v>862163</v>
       </c>
       <c r="R3" t="n">
-        <v>7320682</v>
+        <v>7320205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125098833</v>
+        <v>125098864</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862019</v>
+        <v>862123</v>
       </c>
       <c r="R4" t="n">
-        <v>7320667</v>
+        <v>7320241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125098842</v>
+        <v>125098833</v>
       </c>
       <c r="B5" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1185,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125098838</v>
+        <v>125098842</v>
       </c>
       <c r="B7" t="n">
-        <v>79795</v>
+        <v>92285</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1198,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862155</v>
+        <v>862019</v>
       </c>
       <c r="R7" t="n">
-        <v>7320212</v>
+        <v>7320667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125098836</v>
+        <v>125098871</v>
       </c>
       <c r="B8" t="n">
-        <v>79795</v>
+        <v>92287</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1300,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862163</v>
+        <v>862032</v>
       </c>
       <c r="R8" t="n">
-        <v>7320205</v>
+        <v>7320708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125098864</v>
+        <v>125098838</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>79795</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1406,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862123</v>
+        <v>862155</v>
       </c>
       <c r="R9" t="n">
-        <v>7320241</v>
+        <v>7320212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,7 +1474,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125098864</v>
+        <v>125098838</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>79795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862123</v>
+        <v>862155</v>
       </c>
       <c r="R4" t="n">
-        <v>7320241</v>
+        <v>7320212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125098833</v>
+        <v>125098871</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862019</v>
+        <v>862032</v>
       </c>
       <c r="R5" t="n">
-        <v>7320667</v>
+        <v>7320708</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125098832</v>
+        <v>125098864</v>
       </c>
       <c r="B6" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1096,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862028</v>
+        <v>862123</v>
       </c>
       <c r="R6" t="n">
-        <v>7320659</v>
+        <v>7320241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,6 +1167,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125098842</v>
+        <v>125098832</v>
       </c>
       <c r="B7" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,21 +1202,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862019</v>
+        <v>862028</v>
       </c>
       <c r="R7" t="n">
-        <v>7320667</v>
+        <v>7320659</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125098871</v>
+        <v>125098833</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,21 +1304,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862032</v>
+        <v>862019</v>
       </c>
       <c r="R8" t="n">
-        <v>7320708</v>
+        <v>7320667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125098838</v>
+        <v>125098842</v>
       </c>
       <c r="B9" t="n">
-        <v>79795</v>
+        <v>92285</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1402,25 +1402,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862155</v>
+        <v>862019</v>
       </c>
       <c r="R9" t="n">
-        <v>7320212</v>
+        <v>7320667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125098867</v>
+        <v>125098836</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>79795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862026</v>
+        <v>862163</v>
       </c>
       <c r="R2" t="n">
-        <v>7320682</v>
+        <v>7320205</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125098836</v>
+        <v>125098867</v>
       </c>
       <c r="B3" t="n">
-        <v>79795</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862163</v>
+        <v>862026</v>
       </c>
       <c r="R3" t="n">
-        <v>7320205</v>
+        <v>7320682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125098836</v>
+        <v>125098867</v>
       </c>
       <c r="B2" t="n">
-        <v>79795</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862163</v>
+        <v>862026</v>
       </c>
       <c r="R2" t="n">
-        <v>7320205</v>
+        <v>7320682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125098867</v>
+        <v>125098871</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>92287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862026</v>
+        <v>862032</v>
       </c>
       <c r="R3" t="n">
-        <v>7320682</v>
+        <v>7320708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125098838</v>
+        <v>125098833</v>
       </c>
       <c r="B4" t="n">
-        <v>79795</v>
+        <v>92321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862155</v>
+        <v>862019</v>
       </c>
       <c r="R4" t="n">
-        <v>7320212</v>
+        <v>7320667</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125098871</v>
+        <v>125098842</v>
       </c>
       <c r="B5" t="n">
-        <v>92287</v>
+        <v>92285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862032</v>
+        <v>862019</v>
       </c>
       <c r="R5" t="n">
-        <v>7320708</v>
+        <v>7320667</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125098864</v>
+        <v>125098832</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862123</v>
+        <v>862028</v>
       </c>
       <c r="R6" t="n">
-        <v>7320241</v>
+        <v>7320659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1186,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125098832</v>
+        <v>125098838</v>
       </c>
       <c r="B7" t="n">
-        <v>92321</v>
+        <v>79795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862028</v>
+        <v>862155</v>
       </c>
       <c r="R7" t="n">
-        <v>7320659</v>
+        <v>7320212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125098833</v>
+        <v>125098836</v>
       </c>
       <c r="B8" t="n">
-        <v>92321</v>
+        <v>79795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862019</v>
+        <v>862163</v>
       </c>
       <c r="R8" t="n">
-        <v>7320667</v>
+        <v>7320205</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125098842</v>
+        <v>125098864</v>
       </c>
       <c r="B9" t="n">
-        <v>92285</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1402,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862019</v>
+        <v>862123</v>
       </c>
       <c r="R9" t="n">
-        <v>7320667</v>
+        <v>7320241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,6 +1473,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125098867</v>
+        <v>125098833</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862026</v>
+        <v>862019</v>
       </c>
       <c r="R2" t="n">
-        <v>7320682</v>
+        <v>7320667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125098871</v>
+        <v>125098867</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862032</v>
+        <v>862026</v>
       </c>
       <c r="R3" t="n">
-        <v>7320708</v>
+        <v>7320682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125098833</v>
+        <v>125098838</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>79795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862019</v>
+        <v>862155</v>
       </c>
       <c r="R4" t="n">
-        <v>7320667</v>
+        <v>7320212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125098842</v>
+        <v>125098864</v>
       </c>
       <c r="B5" t="n">
-        <v>92285</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862019</v>
+        <v>862123</v>
       </c>
       <c r="R5" t="n">
-        <v>7320667</v>
+        <v>7320241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1065,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125098832</v>
+        <v>125098836</v>
       </c>
       <c r="B6" t="n">
-        <v>92321</v>
+        <v>79795</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1096,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862028</v>
+        <v>862163</v>
       </c>
       <c r="R6" t="n">
-        <v>7320659</v>
+        <v>7320205</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125098838</v>
+        <v>125098842</v>
       </c>
       <c r="B7" t="n">
-        <v>79795</v>
+        <v>92285</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1198,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862155</v>
+        <v>862019</v>
       </c>
       <c r="R7" t="n">
-        <v>7320212</v>
+        <v>7320667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125098836</v>
+        <v>125098832</v>
       </c>
       <c r="B8" t="n">
-        <v>79795</v>
+        <v>92321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1300,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862163</v>
+        <v>862028</v>
       </c>
       <c r="R8" t="n">
-        <v>7320205</v>
+        <v>7320659</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125098864</v>
+        <v>125098871</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>92287</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1402,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862123</v>
+        <v>862032</v>
       </c>
       <c r="R9" t="n">
-        <v>7320241</v>
+        <v>7320708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,7 +1474,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125098833</v>
+        <v>125098842</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125098867</v>
+        <v>125098833</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>92476</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862026</v>
+        <v>862019</v>
       </c>
       <c r="R3" t="n">
-        <v>7320682</v>
+        <v>7320667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125098838</v>
+        <v>125098867</v>
       </c>
       <c r="B4" t="n">
-        <v>79795</v>
+        <v>92448</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862155</v>
+        <v>862026</v>
       </c>
       <c r="R4" t="n">
-        <v>7320212</v>
+        <v>7320682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125098864</v>
+        <v>125098838</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>79932</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862123</v>
+        <v>862155</v>
       </c>
       <c r="R5" t="n">
-        <v>7320241</v>
+        <v>7320212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,7 +1086,7 @@
         <v>125098836</v>
       </c>
       <c r="B6" t="n">
-        <v>79795</v>
+        <v>79932</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125098842</v>
+        <v>125098864</v>
       </c>
       <c r="B7" t="n">
-        <v>92285</v>
+        <v>92448</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862019</v>
+        <v>862123</v>
       </c>
       <c r="R7" t="n">
-        <v>7320667</v>
+        <v>7320241</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,6 +1269,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125098832</v>
+        <v>125098871</v>
       </c>
       <c r="B8" t="n">
-        <v>92321</v>
+        <v>92442</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,21 +1304,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862028</v>
+        <v>862032</v>
       </c>
       <c r="R8" t="n">
-        <v>7320659</v>
+        <v>7320708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125098871</v>
+        <v>125098832</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>92476</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,21 +1406,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862032</v>
+        <v>862028</v>
       </c>
       <c r="R9" t="n">
-        <v>7320708</v>
+        <v>7320659</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125098842</v>
+        <v>125098864</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92448</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862019</v>
+        <v>862123</v>
       </c>
       <c r="R2" t="n">
-        <v>7320667</v>
+        <v>7320241</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125098833</v>
+        <v>125098867</v>
       </c>
       <c r="B3" t="n">
-        <v>92476</v>
+        <v>92448</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +790,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862019</v>
+        <v>862026</v>
       </c>
       <c r="R3" t="n">
-        <v>7320667</v>
+        <v>7320682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125098867</v>
+        <v>125098833</v>
       </c>
       <c r="B4" t="n">
-        <v>92448</v>
+        <v>92476</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +892,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862026</v>
+        <v>862019</v>
       </c>
       <c r="R4" t="n">
-        <v>7320682</v>
+        <v>7320667</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125098838</v>
+        <v>125098832</v>
       </c>
       <c r="B5" t="n">
-        <v>79932</v>
+        <v>92476</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +994,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862155</v>
+        <v>862028</v>
       </c>
       <c r="R5" t="n">
-        <v>7320212</v>
+        <v>7320659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125098836</v>
+        <v>125098871</v>
       </c>
       <c r="B6" t="n">
-        <v>79932</v>
+        <v>92442</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1096,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862163</v>
+        <v>862032</v>
       </c>
       <c r="R6" t="n">
-        <v>7320205</v>
+        <v>7320708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125098864</v>
+        <v>125098842</v>
       </c>
       <c r="B7" t="n">
-        <v>92448</v>
+        <v>92440</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1198,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862123</v>
+        <v>862019</v>
       </c>
       <c r="R7" t="n">
-        <v>7320241</v>
+        <v>7320667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1270,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125098871</v>
+        <v>125098836</v>
       </c>
       <c r="B8" t="n">
-        <v>92442</v>
+        <v>79932</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,25 +1300,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862032</v>
+        <v>862163</v>
       </c>
       <c r="R8" t="n">
-        <v>7320708</v>
+        <v>7320205</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125098832</v>
+        <v>125098838</v>
       </c>
       <c r="B9" t="n">
-        <v>92476</v>
+        <v>79932</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1402,25 +1402,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862028</v>
+        <v>862155</v>
       </c>
       <c r="R9" t="n">
-        <v>7320659</v>
+        <v>7320212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125098864</v>
+        <v>125098871</v>
       </c>
       <c r="B2" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862123</v>
+        <v>862032</v>
       </c>
       <c r="R2" t="n">
-        <v>7320241</v>
+        <v>7320708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125098867</v>
+        <v>125098864</v>
       </c>
       <c r="B3" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862026</v>
+        <v>862123</v>
       </c>
       <c r="R3" t="n">
-        <v>7320682</v>
+        <v>7320241</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,15 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125098833</v>
+        <v>125098832</v>
       </c>
       <c r="B4" t="n">
-        <v>92476</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862019</v>
+        <v>862028</v>
       </c>
       <c r="R4" t="n">
-        <v>7320667</v>
+        <v>7320659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,37 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125098832</v>
+        <v>125098838</v>
       </c>
       <c r="B5" t="n">
-        <v>92476</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862028</v>
+        <v>862155</v>
       </c>
       <c r="R5" t="n">
-        <v>7320659</v>
+        <v>7320212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,15 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125098871</v>
+        <v>125098842</v>
       </c>
       <c r="B6" t="n">
-        <v>92442</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862032</v>
+        <v>862019</v>
       </c>
       <c r="R6" t="n">
-        <v>7320708</v>
+        <v>7320667</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,37 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125098842</v>
+        <v>125098836</v>
       </c>
       <c r="B7" t="n">
-        <v>92440</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862019</v>
+        <v>862163</v>
       </c>
       <c r="R7" t="n">
-        <v>7320667</v>
+        <v>7320205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,37 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125098836</v>
+        <v>125098833</v>
       </c>
       <c r="B8" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862163</v>
+        <v>862019</v>
       </c>
       <c r="R8" t="n">
-        <v>7320205</v>
+        <v>7320667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,15 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125098838</v>
+        <v>125098867</v>
       </c>
       <c r="B9" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1406,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862155</v>
+        <v>862026</v>
       </c>
       <c r="R9" t="n">
-        <v>7320212</v>
+        <v>7320682</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,6 +1450,976 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125975091</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Degerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>861963</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7320526</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125975090</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Degerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>861908</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7320497</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125975086</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Degerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>862000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7320331</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125975094</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Degerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>862108</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7320256</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125975083</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Degerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>862041</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7320596</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125975097</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Degerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>861926</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7320422</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125975092</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Degerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>861987</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7320584</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125975088</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105355</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Degerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>862111</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7320311</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125975093</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Degerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>862110</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7320271</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125975084</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Degerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>862033</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7320316</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>125975091</v>
       </c>
       <c r="B10" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>125975090</v>
       </c>
       <c r="B11" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,32 +1743,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125975094</v>
+        <v>125975083</v>
       </c>
       <c r="B13" t="n">
-        <v>92509</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862108</v>
+        <v>862041</v>
       </c>
       <c r="R13" t="n">
-        <v>7320256</v>
+        <v>7320596</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125975083</v>
+        <v>125975094</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>92510</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862041</v>
+        <v>862108</v>
       </c>
       <c r="R14" t="n">
-        <v>7320596</v>
+        <v>7320256</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1940,7 +1940,7 @@
         <v>125975097</v>
       </c>
       <c r="B15" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>125975092</v>
       </c>
       <c r="B16" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>125975088</v>
       </c>
       <c r="B17" t="n">
-        <v>105355</v>
+        <v>105356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>125975093</v>
       </c>
       <c r="B18" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>125975091</v>
       </c>
       <c r="B10" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>125975090</v>
       </c>
       <c r="B11" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,32 +1743,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125975083</v>
+        <v>125975094</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>92518</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862041</v>
+        <v>862108</v>
       </c>
       <c r="R13" t="n">
-        <v>7320596</v>
+        <v>7320256</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125975094</v>
+        <v>125975083</v>
       </c>
       <c r="B14" t="n">
-        <v>92510</v>
+        <v>57648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862108</v>
+        <v>862041</v>
       </c>
       <c r="R14" t="n">
-        <v>7320256</v>
+        <v>7320596</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1940,7 +1940,7 @@
         <v>125975097</v>
       </c>
       <c r="B15" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>125975092</v>
       </c>
       <c r="B16" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>125975088</v>
       </c>
       <c r="B17" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>125975093</v>
       </c>
       <c r="B18" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>125975091</v>
       </c>
       <c r="B10" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>125975090</v>
       </c>
       <c r="B11" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>125975094</v>
       </c>
       <c r="B13" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>125975097</v>
       </c>
       <c r="B15" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>125975092</v>
       </c>
       <c r="B16" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>125975088</v>
       </c>
       <c r="B17" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>125975093</v>
       </c>
       <c r="B18" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125975092</v>
+        <v>125975088</v>
       </c>
       <c r="B16" t="n">
-        <v>92522</v>
+        <v>105362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>861987</v>
+        <v>862111</v>
       </c>
       <c r="R16" t="n">
-        <v>7320584</v>
+        <v>7320311</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125975088</v>
+        <v>125975092</v>
       </c>
       <c r="B17" t="n">
-        <v>105362</v>
+        <v>92522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>862111</v>
+        <v>861987</v>
       </c>
       <c r="R17" t="n">
-        <v>7320311</v>
+        <v>7320584</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125975088</v>
+        <v>125975092</v>
       </c>
       <c r="B16" t="n">
-        <v>105362</v>
+        <v>92522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862111</v>
+        <v>861987</v>
       </c>
       <c r="R16" t="n">
-        <v>7320311</v>
+        <v>7320584</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125975092</v>
+        <v>125975088</v>
       </c>
       <c r="B17" t="n">
-        <v>92522</v>
+        <v>105363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>861987</v>
+        <v>862111</v>
       </c>
       <c r="R17" t="n">
-        <v>7320584</v>
+        <v>7320311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>125975091</v>
       </c>
       <c r="B10" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>125975090</v>
       </c>
       <c r="B11" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>125975086</v>
       </c>
       <c r="B12" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>125975094</v>
       </c>
       <c r="B13" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>125975083</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>125975097</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>125975092</v>
       </c>
       <c r="B16" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>125975088</v>
       </c>
       <c r="B17" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>125975093</v>
       </c>
       <c r="B18" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>125975084</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>125975091</v>
       </c>
       <c r="B10" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>125975090</v>
       </c>
       <c r="B11" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,32 +1743,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125975094</v>
+        <v>125975083</v>
       </c>
       <c r="B13" t="n">
-        <v>92524</v>
+        <v>57649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862108</v>
+        <v>862041</v>
       </c>
       <c r="R13" t="n">
-        <v>7320256</v>
+        <v>7320596</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125975083</v>
+        <v>125975094</v>
       </c>
       <c r="B14" t="n">
-        <v>57649</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862041</v>
+        <v>862108</v>
       </c>
       <c r="R14" t="n">
-        <v>7320596</v>
+        <v>7320256</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1940,7 +1940,7 @@
         <v>125975097</v>
       </c>
       <c r="B15" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>125975092</v>
       </c>
       <c r="B16" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>125975088</v>
       </c>
       <c r="B17" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>125975093</v>
       </c>
       <c r="B18" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>125975091</v>
       </c>
       <c r="B10" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>125975090</v>
       </c>
       <c r="B11" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,32 +1743,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125975083</v>
+        <v>125975094</v>
       </c>
       <c r="B13" t="n">
-        <v>57649</v>
+        <v>92528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862041</v>
+        <v>862108</v>
       </c>
       <c r="R13" t="n">
-        <v>7320596</v>
+        <v>7320256</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125975094</v>
+        <v>125975083</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>57649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862108</v>
+        <v>862041</v>
       </c>
       <c r="R14" t="n">
-        <v>7320256</v>
+        <v>7320596</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1940,7 +1940,7 @@
         <v>125975097</v>
       </c>
       <c r="B15" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125975092</v>
+        <v>125975088</v>
       </c>
       <c r="B16" t="n">
-        <v>92526</v>
+        <v>105371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>861987</v>
+        <v>862111</v>
       </c>
       <c r="R16" t="n">
-        <v>7320584</v>
+        <v>7320311</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125975088</v>
+        <v>125975092</v>
       </c>
       <c r="B17" t="n">
-        <v>105367</v>
+        <v>92528</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>862111</v>
+        <v>861987</v>
       </c>
       <c r="R17" t="n">
-        <v>7320311</v>
+        <v>7320584</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2231,7 +2231,7 @@
         <v>125975093</v>
       </c>
       <c r="B18" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125975088</v>
+        <v>125975092</v>
       </c>
       <c r="B16" t="n">
-        <v>105371</v>
+        <v>92528</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862111</v>
+        <v>861987</v>
       </c>
       <c r="R16" t="n">
-        <v>7320311</v>
+        <v>7320584</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125975092</v>
+        <v>125975088</v>
       </c>
       <c r="B17" t="n">
-        <v>92528</v>
+        <v>105371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>861987</v>
+        <v>862111</v>
       </c>
       <c r="R17" t="n">
-        <v>7320584</v>
+        <v>7320311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>125975091</v>
       </c>
       <c r="B10" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>125975090</v>
       </c>
       <c r="B11" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>125975086</v>
       </c>
       <c r="B12" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>125975094</v>
       </c>
       <c r="B13" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>125975083</v>
       </c>
       <c r="B14" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>125975097</v>
       </c>
       <c r="B15" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>125975092</v>
       </c>
       <c r="B16" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>125975088</v>
       </c>
       <c r="B17" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>125975093</v>
       </c>
       <c r="B18" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>125975084</v>
       </c>
       <c r="B19" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -1743,32 +1743,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125975094</v>
+        <v>125975083</v>
       </c>
       <c r="B13" t="n">
-        <v>92532</v>
+        <v>57653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862108</v>
+        <v>862041</v>
       </c>
       <c r="R13" t="n">
-        <v>7320256</v>
+        <v>7320596</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125975083</v>
+        <v>125975094</v>
       </c>
       <c r="B14" t="n">
-        <v>57653</v>
+        <v>92532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862041</v>
+        <v>862108</v>
       </c>
       <c r="R14" t="n">
-        <v>7320596</v>
+        <v>7320256</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2134,7 +2134,7 @@
         <v>125975088</v>
       </c>
       <c r="B17" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -1455,7 +1455,7 @@
         <v>125975091</v>
       </c>
       <c r="B10" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>125975090</v>
       </c>
       <c r="B11" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>125975086</v>
       </c>
       <c r="B12" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,32 +1743,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125975083</v>
+        <v>125975094</v>
       </c>
       <c r="B13" t="n">
-        <v>57653</v>
+        <v>92535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862041</v>
+        <v>862108</v>
       </c>
       <c r="R13" t="n">
-        <v>7320596</v>
+        <v>7320256</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125975094</v>
+        <v>125975083</v>
       </c>
       <c r="B14" t="n">
-        <v>92532</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862108</v>
+        <v>862041</v>
       </c>
       <c r="R14" t="n">
-        <v>7320256</v>
+        <v>7320596</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1940,7 +1940,7 @@
         <v>125975097</v>
       </c>
       <c r="B15" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125975092</v>
+        <v>125975088</v>
       </c>
       <c r="B16" t="n">
-        <v>92532</v>
+        <v>105396</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>861987</v>
+        <v>862111</v>
       </c>
       <c r="R16" t="n">
-        <v>7320584</v>
+        <v>7320311</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125975088</v>
+        <v>125975092</v>
       </c>
       <c r="B17" t="n">
-        <v>105387</v>
+        <v>92535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>862111</v>
+        <v>861987</v>
       </c>
       <c r="R17" t="n">
-        <v>7320311</v>
+        <v>7320584</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2231,7 +2231,7 @@
         <v>125975093</v>
       </c>
       <c r="B18" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>125975084</v>
       </c>
       <c r="B19" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11762-2025 artfynd.xlsx
+++ b/artfynd/A 11762-2025 artfynd.xlsx
@@ -2034,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125975088</v>
+        <v>125975092</v>
       </c>
       <c r="B16" t="n">
-        <v>105396</v>
+        <v>92535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862111</v>
+        <v>861987</v>
       </c>
       <c r="R16" t="n">
-        <v>7320311</v>
+        <v>7320584</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125975092</v>
+        <v>125975088</v>
       </c>
       <c r="B17" t="n">
-        <v>92535</v>
+        <v>105396</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>861987</v>
+        <v>862111</v>
       </c>
       <c r="R17" t="n">
-        <v>7320584</v>
+        <v>7320311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
